--- a/doc/async_fifo_testplan.xlsx
+++ b/doc/async_fifo_testplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriyansh\Asynchronous-FIFO\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C06F9F6-CB33-4379-8A89-337976B2A13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8BFFDB-CD0A-46DE-8F17-17820C7EB09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{02E35841-84F1-420D-8850-A09C6E102933}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02E35841-84F1-420D-8850-A09C6E102933}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFO Testplan" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>Category</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Fill FIFO with data, assert reset mid-operation, verify fifo_empty=1 and fifo_full=0 during reset, deassert reset, write+read new data to verify clean recovery</t>
-  </si>
-  <si>
-    <t>Implemented</t>
   </si>
   <si>
     <t>test_reset_when_empty</t>
@@ -397,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -435,7 +432,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -760,7 +756,7 @@
     <col min="5" max="5" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -790,468 +786,412 @@
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="C23" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="D27" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="E27" s="12"/>
     </row>
     <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="D28" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="D29" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="E29" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E29" xr:uid="{767AEE8B-C75E-42B0-B60C-78946259574D}"/>
